--- a/2025_Ticket_Sample.xlsx
+++ b/2025_Ticket_Sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CraigHorn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C901700-A19A-4438-80DF-2546C6BEB336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E00E60-78F1-4E54-B26F-49D8F218AF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9810" yWindow="1590" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1080" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="field ticket" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <r>
       <t xml:space="preserve">DELIVERY TICKET     </t>
@@ -145,9 +145,6 @@
     <t xml:space="preserve">JOB DESCRIPTION  </t>
   </si>
   <si>
-    <t>6'' Layflat Rental</t>
-  </si>
-  <si>
     <t>LENGTH TIME</t>
   </si>
   <si>
@@ -164,15 +161,6 @@
   </si>
   <si>
     <t>AMOUNT</t>
-  </si>
-  <si>
-    <t>Setup</t>
-  </si>
-  <si>
-    <t>Day Rate 8/19-10/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teardown </t>
   </si>
   <si>
     <t>ELEVATE ENERGY SERVICES, LLC</t>
@@ -548,6 +536,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -563,24 +590,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -612,33 +627,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1014,215 +1002,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="21"/>
+      <c r="F1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="34"/>
       <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="4" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="47"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="C12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="D12" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="42" t="s">
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="20" t="s">
+      <c r="H12" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14"/>
-      <c r="B13" s="10">
-        <v>1</v>
-      </c>
+      <c r="B13" s="10"/>
       <c r="C13" s="10"/>
-      <c r="D13" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="6">
-        <v>1000</v>
-      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="15">
         <f t="shared" ref="H13" si="0">G13*B13</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14"/>
-      <c r="B14" s="10">
-        <v>47</v>
-      </c>
+      <c r="B14" s="10"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="6">
-        <v>100</v>
-      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="15">
         <f t="shared" ref="H14:H17" si="1">G14*B14</f>
-        <v>4700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14"/>
-      <c r="B15" s="10">
-        <v>1</v>
-      </c>
+      <c r="B15" s="10"/>
       <c r="C15" s="10"/>
-      <c r="D15" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="6">
-        <v>1000</v>
-      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="15">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
       <c r="G16" s="6"/>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
@@ -1233,9 +1201,9 @@
       <c r="A17" s="14"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
       <c r="G17" s="6"/>
       <c r="H17" s="15">
         <f t="shared" si="1"/>
@@ -1246,9 +1214,9 @@
       <c r="A18" s="14"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
       <c r="G18" s="6"/>
       <c r="H18" s="15">
         <f t="shared" ref="H18:H19" si="2">G18*B18</f>
@@ -1259,9 +1227,9 @@
       <c r="A19" s="14"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
       <c r="G19" s="6"/>
       <c r="H19" s="15">
         <f t="shared" si="2"/>
@@ -1272,9 +1240,9 @@
       <c r="A20" s="14"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
       <c r="G20" s="6"/>
       <c r="H20" s="15">
         <f t="shared" ref="H20:H21" si="3">G20*B20</f>
@@ -1285,9 +1253,9 @@
       <c r="A21" s="14"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
       <c r="G21" s="6"/>
       <c r="H21" s="15">
         <f t="shared" si="3"/>
@@ -1298,9 +1266,9 @@
       <c r="A22" s="14"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
       <c r="G22" s="6"/>
       <c r="H22" s="15">
         <f t="shared" ref="H22:H23" si="4">G22*B22</f>
@@ -1311,9 +1279,9 @@
       <c r="A23" s="14"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="31"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
       <c r="G23" s="6"/>
       <c r="H23" s="15">
         <f t="shared" si="4"/>
@@ -1324,12 +1292,12 @@
       <c r="A24" s="14"/>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="31"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
       <c r="G24" s="6"/>
       <c r="H24" s="15">
-        <f t="shared" ref="H24" si="5">G24*B24</f>
+        <f t="shared" ref="H24:H30" si="5">G24*B24</f>
         <v>0</v>
       </c>
     </row>
@@ -1337,141 +1305,137 @@
       <c r="A25" s="14"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="15"/>
+      <c r="H25" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="14"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="15"/>
+      <c r="H26" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="15"/>
+      <c r="H27" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="31"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="15"/>
+      <c r="H28" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="16"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="15"/>
+      <c r="H29" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="15"/>
+      <c r="H30" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="41"/>
+      <c r="A31" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="50"/>
       <c r="G31" s="18" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H31" s="19">
         <f>SUM(H13:H30)</f>
-        <v>6700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="G32" s="27"/>
-      <c r="H32" s="28"/>
+      <c r="A32" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
     </row>
     <row r="33" spans="1:8" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="36"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="G33" s="27"/>
-      <c r="H33" s="28"/>
+      <c r="A33" s="45"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="39"/>
+      <c r="H33" s="40"/>
     </row>
     <row r="34" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25"/>
+      <c r="A34" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A34:H34"/>
@@ -1488,6 +1452,28 @@
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F7:H7"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -1499,15 +1485,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6bde121e-b1b8-4598-8a21-591b7be5a480" xsi:nil="true"/>
@@ -1516,6 +1493,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1712,20 +1698,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B48E121-E85B-4630-BA7A-4922D15A2FD8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{005D6C26-8D75-43AB-8523-EB2B675EC93B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="6bde121e-b1b8-4598-8a21-591b7be5a480"/>
     <ds:schemaRef ds:uri="b101623d-cb95-4b64-96da-3d9b698a2935"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B48E121-E85B-4630-BA7A-4922D15A2FD8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/2025_Ticket_Sample.xlsx
+++ b/2025_Ticket_Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CraigHorn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E00E60-78F1-4E54-B26F-49D8F218AF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC917DD9-6963-492A-99FA-2197D4B09F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1080" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7950" yWindow="6255" windowWidth="28965" windowHeight="16320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="field ticket" sheetId="1" r:id="rId1"/>
@@ -120,14 +120,53 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">COUNTY AND STATE </t>
-  </si>
-  <si>
     <t>ORDERED BY</t>
   </si>
   <si>
+    <t xml:space="preserve">DEPARTMENT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOB DESCRIPTION  </t>
+  </si>
+  <si>
+    <t>LENGTH TIME</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>UNIT PRICE</t>
+  </si>
+  <si>
+    <t>AMOUNT</t>
+  </si>
+  <si>
+    <t>ELEVATE ENERGY SERVICES, LLC</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>WELL CODING (PLEASE STAMP AND CODE HERE)</t>
+  </si>
+  <si>
+    <t>Customer Name Print</t>
+  </si>
+  <si>
+    <t>Customer Signature</t>
+  </si>
+  <si>
+    <t>Any applicable taxes will be applied at time of invoicing.</t>
+  </si>
+  <si>
     <r>
-      <t>LOCATION</t>
+      <t>JOB NAME</t>
     </r>
     <r>
       <rPr>
@@ -139,46 +178,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">DEPARTMENT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOB DESCRIPTION  </t>
-  </si>
-  <si>
-    <t>LENGTH TIME</t>
-  </si>
-  <si>
-    <t>QTY</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>DESCRIPTION</t>
-  </si>
-  <si>
-    <t>UNIT PRICE</t>
-  </si>
-  <si>
-    <t>AMOUNT</t>
-  </si>
-  <si>
-    <t>ELEVATE ENERGY SERVICES, LLC</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>WELL CODING (PLEASE STAMP AND CODE HERE)</t>
-  </si>
-  <si>
-    <t>Customer Name Print</t>
-  </si>
-  <si>
-    <t>Customer Signature</t>
-  </si>
-  <si>
-    <t>Any applicable taxes will be applied at time of invoicing.</t>
+    <t xml:space="preserve">COUNTY, STATE </t>
   </si>
 </sst>
 </file>
@@ -494,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -505,8 +505,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -536,6 +534,72 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -560,75 +624,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1002,440 +999,463 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="34"/>
+      <c r="F1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="19"/>
       <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
     </row>
     <row r="4" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
       <c r="E6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="28"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="48"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+        <v>25</v>
+      </c>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="3" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
-    </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="3" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
+    </row>
+    <row r="11" spans="1:8" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="3" t="s">
+      <c r="B11" s="43"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="45"/>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
-    </row>
-    <row r="11" spans="1:8" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="B12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="C12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="D12" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="H12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="29"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="15">
+      <c r="H13" s="13">
         <f t="shared" ref="H13" si="0">G13*B13</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="29"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="15">
+      <c r="H14" s="13">
         <f t="shared" ref="H14:H17" si="1">G14*B14</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="14"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="32"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="29"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="15">
+      <c r="H15" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="32"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="29"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="15">
+      <c r="H16" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="14"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="29"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="15">
+      <c r="H17" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="29"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="15">
+      <c r="H18" s="13">
         <f t="shared" ref="H18:H19" si="2">G18*B18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="29"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="15">
+      <c r="H19" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="29"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="15">
+      <c r="H20" s="13">
         <f t="shared" ref="H20:H21" si="3">G20*B20</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="29"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="15">
+      <c r="H21" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="29"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="15">
+      <c r="H22" s="13">
         <f t="shared" ref="H22:H23" si="4">G22*B22</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="29"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="15">
+      <c r="H23" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="14"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="29"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="15">
+      <c r="H24" s="13">
         <f t="shared" ref="H24:H30" si="5">G24*B24</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="15">
+      <c r="H25" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="14"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="15">
+      <c r="H26" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="29"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="15">
+      <c r="H27" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="14"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="29"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="15">
+      <c r="H28" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="16"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="15">
+      <c r="H29" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="17"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="15">
+      <c r="H30" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="17">
+        <f>SUM(H13:H30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="18" t="s">
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="19">
-        <f>SUM(H13:H30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="42" t="s">
+      <c r="G32" s="25"/>
+      <c r="H32" s="26"/>
+    </row>
+    <row r="33" spans="1:8" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="34"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="39" t="s">
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
+    </row>
+    <row r="34" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="39"/>
-      <c r="H32" s="40"/>
-    </row>
-    <row r="33" spans="1:8" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="45"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" s="39"/>
-      <c r="H33" s="40"/>
-    </row>
-    <row r="34" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="38"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A34:H34"/>
@@ -1452,28 +1472,6 @@
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F7:H7"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -1485,26 +1483,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6bde121e-b1b8-4598-8a21-591b7be5a480" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b101623d-cb95-4b64-96da-3d9b698a2935">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010010CF9B77C0D74248B805737DC8D30F3B" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="063025790e04971f42e64f1f8088a717">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b101623d-cb95-4b64-96da-3d9b698a2935" xmlns:ns3="6bde121e-b1b8-4598-8a21-591b7be5a480" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3334b72f699798deb8d92700402de3a4" ns2:_="" ns3:_="">
     <xsd:import namespace="b101623d-cb95-4b64-96da-3d9b698a2935"/>
@@ -1697,26 +1675,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{005D6C26-8D75-43AB-8523-EB2B675EC93B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6bde121e-b1b8-4598-8a21-591b7be5a480"/>
-    <ds:schemaRef ds:uri="b101623d-cb95-4b64-96da-3d9b698a2935"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B48E121-E85B-4630-BA7A-4922D15A2FD8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6bde121e-b1b8-4598-8a21-591b7be5a480" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b101623d-cb95-4b64-96da-3d9b698a2935">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A47DB3FF-1FD1-4BEF-BCC7-619E5BF3A9E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1733,4 +1712,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B48E121-E85B-4630-BA7A-4922D15A2FD8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{005D6C26-8D75-43AB-8523-EB2B675EC93B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6bde121e-b1b8-4598-8a21-591b7be5a480"/>
+    <ds:schemaRef ds:uri="b101623d-cb95-4b64-96da-3d9b698a2935"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>